--- a/erp-server/erp-server-file/src/main/resources/excel/mrp/deliverySuggestion.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/mrp/deliverySuggestion.xlsx
@@ -113,7 +113,7 @@
     <t>{.logisticsCost}</t>
   </si>
   <si>
-    <t>{.createTypeName}</t>
+    <t>{.dataTypeName}</t>
   </si>
   <si>
     <t>{.createUserName}</t>
